--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0009.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0009.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Đừng khóc, Ku-Lolo! Nếu có kẻ xấu, tức là đã đến lúc anh hùng xuất hiện rồi! Chiến binh Cừu Lông và Chiến binh Black Cat ngầu lòi sẽ cứu nguy, phải không nào?</t>
+          <t>Đừng khóc, Ku-Lolo! Nếu có kẻ xấu, tức là đã đến lúc anh hùng xuất hiện rồi! Chiến binh Cừu Lông và Chiến binh Mèo Đen ngầu lòi sẽ cứu nguy, phải không nào?</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Ê! Nói rõ cho nghe nè, đó là một Abby khác. Tethys nhỏ bé kia làm sao mà sao chép được một Echo như ta! Let's go, {PlayerName}. Chúng ta sẽ tự mình săn lùng thằng "Abbowser" này!</t>
+          <t>Ê! Nói rõ cho nghe nè, đó là một Abby khác. Tethys nhỏ bé kia làm sao mà sao chép được một Echo như tao! Đi nào, {PlayerName}. Chúng ta sẽ tự mình săn lùng thằng "Abbowser" này!</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Và để thoát khỏi đây, chúng ta cần giải cứu những người bạn &lt;te href=800004&gt;Cube&lt;/te&gt; bị phân tán, đánh bại Abbowser, và làm lại... &lt;ano=Control Unit&gt;&lt;te href=800002&gt;Bánh Kem Kỷ Niệm&lt;/te&gt;&lt;/ano&gt;?</t>
+          <t>Để thoát khỏi đây, chúng ta cần giải cứu những &lt;te href=800004&gt;Khối Lập Phương&lt;/te&gt; bị thất lạc, đánh bại Abbowser, rồi làm lại... &lt;ano=Control Unit&gt;&lt;te href=800002&gt;Bánh Sinh Nhật&lt;/te&gt;&lt;/ano&gt;?</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Tuy nhiên, một thực thể kỳ lạ tự xưng là "Abbowser" đã nhanh chóng chặn &lt;te href=800007&gt;Kênh&lt;/te&gt; lại. Tôi chỉ kịp truyền đi một lượng dữ liệu bằng kích thước của một Khối Remnant.</t>
+          <t>Tuy nhiên, một thực thể kỳ lạ tự xưng là "Abbowser" đã nhanh chóng chặn &lt;te href=800007&gt;Kênh&lt;/te&gt; lại. Tôi chỉ kịp truyền đi một lượng dữ liệu bằng kích thước của một Khối Tàn Tích.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Tại Abbowser Castle, cậu phát hiện một nơi rất giống Black Shores. Hóa ra Camellya Cube và Abbowser đã cùng nhau tạo ra "Black Shores New"! Giờ đây, Camellya Cube đang nắm quyền điều khiển trò chơi. Nếu cô ấy không vui, mọi chuyện có thể sẽ rất tệ.</t>
+          <t>Tại Lâu Đài Abbowser, cậu phát hiện một nơi rất giống Bờ Biển Đen. Hóa ra Camellya Cube và Abbowser đã cùng nhau tạo ra "Bờ Biển Đen Mới"! Giờ đây, Camellya Cube đang nắm quyền điều khiển trò chơi. Nếu cô ấy không vui, mọi chuyện có thể sẽ rất tệ.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A, ngài Abbowser. Xin lỗi vì lần trước không kịp giới thiệu bản thân cho tử tế, mọi chuyện diễn ra quá nhanh. Thật ra ta là dân chuyên phá ngục đấy.</t>
+          <t>A, ngài Abbowser. Xin lỗi vì lần trước không kịp giới thiệu bản thân cho tử tế, mọi chuyện diễn ra quá nhanh. Thật ra tao là dân chuyên phá ngục đấy.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Cuộc thương lượng giữa Abbowser và Carlotta đang hoàn toàn bế tắc. Sự xuất hiện của cậu đã làm thay đổi cục diện. Không có tay chân hay Echoes hỗ trợ, Abbowser đã bị dồn vào đường cùng và thất bại hoàn toàn. Trong khi đó, Carlotta dường như đã tìm ra manh mối dẫn đến các Cube khác ở tầng này.</t>
+          <t>Cuộc thương lượng giữa Abbowser và Carlotta đang hoàn toàn bế tắc. Sự xuất hiện của cậu đã làm thay đổi cục diện. Không có tay chân hay Echo hỗ trợ, Abbowser đã bị dồn vào đường cùng và thất bại hoàn toàn. Trong khi đó, Carlotta dường như đã tìm ra manh mối dẫn đến các Cube khác ở tầng này.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Lại thêm lần nữa, Abbowser chặn đường cậu, lần này hắn dẫn theo tay sai đắc lực Elite Không. 2 - Cantarella. Nhưng trớ trêu thay! Cô ta "lỡ tay" dùng nhầm loại bột, khiến cậu càng mạnh mẽ hơn.</t>
+          <t>Lại thêm lần nữa, Abbowser chặn đường cậu, lần này hắn dẫn theo tay sai đắc lực Elite No. 2 - Cantarella. Nhưng trớ trêu thay! Cô ta "lỡ tay" dùng nhầm loại bột, khiến cậu càng mạnh mẽ hơn.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Làm ơn đi mà! Để tụi nó tự do lang thang với mấy cái Echo đầy rẫy ở mỗi tầng? Nguy hiểm lắm đấy. Kiểu như thằng Brant kia! Nó cứ thế bước vào và tự tiện mở MẤY CÁI RƯƠNG CỦA TÔI!</t>
+          <t>Làm ơn đi mà! Để tụi nó tự do lang thang với mấy cái Tổ Tacet đầy rẫy ở mỗi tầng? Nguy hiểm lắm đấy. Kiểu như thằng Brant kia! Nó cứ thế bước vào và tự tiện mở MẤY CÁI RƯƠNG CỦA TÔI!</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>À đúng rồi, còn mấy Echo đó! Tôi chỉ bảo thiết kế vài thử thách khuyến khích hợp tác để mọi người gần gũi hơn thôi. Sao anh lại đặt mấy Echo nguy hiểm ở đây chứ?!</t>
+          <t>À đúng rồi, còn mấy Tổ Tacet đó! Tôi chỉ bảo thiết kế vài thử thách khuyến khích hợp tác để mọi người gần gũi hơn thôi. Sao anh lại đặt mấy Tổ Tacet nguy hiểm ở đây chứ?!</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Ừ, tớ biết. Đầu óc giờ nhẹ tênh, chẳng còn những tiếng nói phiền nhiễu, tất nhiên đây không phải con người thật của tớ. Nhưng tớ không quan tâm. {Male=Hắn;Female=Cô ấy} mới là thật mà, đúng chứ?</t>
+          <t>Ừ, tớ biết. Đầu óc giờ nhẹ tênh, chẳng còn những tiếng nói phiền nhiễu, tất nhiên đây không phải con người thật của tớ. Nhưng tớ không quan tâm. {Male=He;Female=She} mới là thật mà, đúng chứ?</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Bởi vì chính ta đã biến cậu thành một! Bà Thủ Hộ Chỉ có thể chia cho ta một chút sức mạnh tính toán của Tethys, nên &lt;te href=800004&gt;Cube&lt;/te&gt; này là thứ tốt nhất ta có thể làm cho cậu.</t>
+          <t>Bởi vì chính ta đã biến cậu thành một! Bà Thủ Hộ Chỉ có thể chia cho ta một chút sức mạnh tính toán của Tethys, nên &lt;te href=800004&gt;Khối Lập Phương&lt;/te&gt; này là thứ tốt nhất ta có thể làm cho cậu.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Khi bước vào Sự Kiện Solaris Trở Lại, cậu kinh ngạc phát hiện mình đã biến thành một Cube. Chưa kịp hiểu chuyện gì xảy ra, chiếc bánh kỷ niệm – bộ điều khiển của trò chơi – đã bị một Cube bí ẩn tên "Abbowser" nuốt chửng!</t>
+          <t>Khi bước vào Sự Kiện Solaris Trở Lại, cậu kinh ngạc phát hiện mình đã biến thành một Khối Lập Phương. Chưa kịp hiểu chuyện gì xảy ra, chiếc bánh kỷ niệm – bộ điều khiển của trò chơi – đã bị một Khối Lập Phương bí ẩn tên "Abbowser" nuốt chửng!</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{PlayerName}, tớ sẽ biến chúng ta thành định dạng Echo và tải dữ liệu vào Terminal của cậu. Sau đó, tớ sẽ kết nối Terminal của cậu với Lâu đài Abbowser để giải phóng sức mạnh của chúng ta.</t>
+          <t>{PlayerName}, tớ sẽ biến chúng ta thành định dạng Echo và tải dữ liệu vào Thiết bị đầu cuối của cậu. Sau đó, tớ sẽ kết nối Thiết bị đầu cuối của cậu với Lâu đài Abbowser để giải phóng sức mạnh của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Terminal của anh ấy đang bị khóa, chỉ gửi tin nhắn trên kênh nội bộ thôi. Cậu thực sự đang khoe kỳ nghỉ trước mặt anh ấy đấy à? Với cả còn đánh dấu KHẨN CẤP nữa?!</t>
+          <t>Thiết bị đầu cuối của anh ấy đang bị khóa, chỉ gửi tin nhắn trên kênh nội bộ thôi. Cậu thực sự đang khoe kỳ nghỉ trước mặt anh ấy đấy à? Với cả còn đánh dấu KHẨN CẤP nữa?!</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Yes. Chính xác hơn, đây là Ragunna vào đêm trước lễ Carnevale. Những lá cờ sặc sỡ, ánh đèn rực rỡ, và đám đông tràn ngập đường phố—tất cả đều y như những gì cậu nhớ.</t>
+          <t>Đúng vậy. Chính xác hơn, đây là Ragunna vào đêm trước lễ Carnevale. Những lá cờ sặc sỡ, ánh đèn rực rỡ, và đám đông tràn ngập đường phố—tất cả đều y như những gì cậu nhớ.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Pháo hoa giấy rơi từ trên cao. Music tràn ngập phố phường. Tiếng cười, tiếng vỗ tay, tiếng reo hò hòa quyện thành bản giao hưởng. Những bóng người vừa thấy lúc trước giờ đã bị nhấn chìm trong dòng người cuồn cuộn.</t>
+          <t>Pháo hoa giấy rơi từ trên cao. Âm nhạc tràn ngập phố phường. Tiếng cười, tiếng vỗ tay, tiếng reo hò hòa quyện thành bản giao hưởng. Những bóng người vừa thấy lúc trước giờ đã bị nhấn chìm trong dòng người cuồn cuộn.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Cậu biết hắn gia nhập một đoàn kịch ngầm cách đây không lâu không? Gần đây bị Hội Án bắt giam, có lẽ sắp bị đưa đến Pilgrim's Sail rồi.</t>
+          <t>Mày biết hắn gia nhập một đoàn kịch ngầm cách đây không lâu không? Gần đây bị Hội Án bắt giam, có lẽ sắp bị đưa đến Pilgrim's Sail rồi.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Dodgem vào một đồng Monnaie, đặt câu hỏi với tấm lòng chân thành, và ngươi sẽ nhận được câu trả lời mình cần: dù là tương lai đang chờ đón hay sự thật về quá khứ ngươi tìm kiếm.</t>
+          <t>Ném vào một đồng Monnaie, đặt câu hỏi với tấm lòng chân thành, và ngươi sẽ nhận được câu trả lời mình cần: dù là tương lai đang chờ đón hay sự thật về quá khứ ngươi tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Không, cậu hiểu nhầm rồi. Trộm cắp thuộc thẩm quyền của Phòng Discipline, nhưng vì cô bé còn nhỏ tuổi, tôi nghĩ Phòng Khai Sáng sẽ xử lý vụ này phù hợp hơn.</t>
+          <t>Không, cậu hiểu nhầm rồi. Trộm cắp thuộc thẩm quyền của Phòng Kỷ Luật, nhưng vì cô bé còn nhỏ tuổi, tôi nghĩ Phòng Khai Sáng sẽ xử lý vụ này phù hợp hơn.</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Ừ, sau đó ta mới nhận ra, một số người ở Fisalia trông có vẻ cứng rắn nhưng thực ra rất tốt bụng. Họ không độc ác như chúng ta vẫn nghĩ đâu.</t>
+          <t>Ừ, sau đó tao mới nhận ra, một số người ở Fisalia trông có vẻ cứng rắn nhưng thực ra rất tốt bụng. Họ không độc ác như chúng ta vẫn nghĩ đâu.</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Tôi biết người bạn này. {Male=Anh ấy;Female=Cô ấy} là khách của Priest Alessio. Chắc hẳn ngài ấy đã ngầm cho phép những lỗi lầm nhỏ này. Chúng ta không còn quyền can thiệp... hãy bình tĩnh lại.</t>
+          <t>Tôi biết người bạn này. {Male=He;Female=She} là khách của Linh mục Alessio. Chắc hẳn ngài ấy đã ngầm cho phép những lỗi lầm nhỏ này. Chúng ta không còn quyền can thiệp... hãy bình tĩnh lại.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>{Male=Hắn;Female=Bả} là Người Chiến Thắng Carnevale phải không? Nếu {Male=hắn;Female=bả} đã được Sentinel chấp thuận, chúng ta nên tỏ lòng kính trọng... Thôi nào, bình tĩnh lại đi.</t>
+          <t>{Male=he;Female=she} là Người Chiến Thắng Carnevale phải không? Nếu {Male=hắn;Female=bả} đã được Sentinel chấp thuận, chúng ta nên tỏ lòng kính trọng... Thôi nào, bình tĩnh lại đi.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Lúc tớ điều tra vụ này, Hội Ánh Sáng đã truy đuổi ráo riết và thậm chí còn cướp luôn Terminal của tớ. May mà nhà Montelli đã ra tay giúp đỡ...</t>
+          <t>Lúc tớ điều tra vụ này, Hội Ánh Sáng đã truy đuổi ráo riết và thậm chí còn cướp luôn Thiết bị đầu cuối của tớ. May mà nhà Montelli đã ra tay giúp đỡ...</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Chính bà Carlotta đã nói với tôi rằng một thành viên của Black Shores sẽ sớm đến Ragunna. Tôi quyết định tìm {Male=anh ấy;Female=cô ấy} ngay và chia sẻ thông tin mình có.</t>
+          <t>Chính bà Carlotta đã nói với tôi rằng một thành viên của Black Shores sẽ sớm đến Ragunna. Tôi quyết định tìm {Male=him;Female=her} ngay và chia sẻ thông tin mình có.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Ta mượn bộ đồ và mặt nạ từ nhà Montelli để hòa vào đám đông, rồi lẻn về thành phố trong lễ Carnevale. Cuối cùng thì công sức của ta cũng được đền đáp.</t>
+          <t>Tao mượn bộ đồ và mặt nạ từ nhà Montelli để hòa vào đám đông, rồi lẻn về thành phố trong lễ Carnevale. Cuối cùng thì công sức của tao cũng được đền đáp.</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Trong lãnh địa Rinascita, một khi tần số của Discord bị phân tán, Reverberation còn sót lại nếu không được thu thập theo thời gian sẽ dần bị Hệ Thống Data Genesis Nexus hấp thụ, trở thành mẫu tần số cho Common Echoes.</t>
+          <t>Trong lãnh địa Rinascita, một khi tần số của Tacet Discord bị phân tán, Reverberation còn sót lại nếu không được thu thập theo thời gian sẽ dần bị Hệ Thống Dữ Liệu Genesis Nexus hấp thụ, trở thành mẫu tần số cho Common Echoes.</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Ta muốn nhắc nhở ngươi rằng gần đây hoạt động của Discord bên ngoài Thành Ragunna đã gia tăng. Nếu ngươi định mạo hiểm vào nơi hoang dã để thu thập Echoes, hãy cẩn thận.</t>
+          <t>Ta muốn nhắc nhở ngươi rằng gần đây hoạt động của Tacet Discord bên ngoài Thành Ragunna đã gia tăng. Nếu ngươi định mạo hiểm vào nơi hoang dã để thu thập Echo, hãy cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Tần số của Vitreum Dancer bắt nguồn từ những ô kính màu trong đống đổ nát. Một số học giả tin rằng tần số của chúng chứa đựng một phần lịch sử liên quan đến Sentinel.</t>
+          <t>Tần số của Vũ Công Pha Lê bắt nguồn từ những ô kính màu trong đống đổ nát. Một số học giả tin rằng tần số của chúng chứa đựng một phần lịch sử liên quan đến Sentinel.</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Nhưng mỗi lần chứng kiến những Vitreum Dancer này, ta lại không khỏi kinh ngạc trước quyền năng của Người Bảo Hộ trên vạn vật... mang những kỳ quan đến cho nhân loại, phô diễn phép màu của Ngài—đó chính là sứ mệnh của ta.</t>
+          <t>Nhưng mỗi lần chứng kiến những Vũ Công Pha Lê này, ta lại không khỏi kinh ngạc trước quyền năng của Người Bảo Hộ trên vạn vật... mang những kỳ quan đến cho nhân loại, phô diễn phép màu của Ngài—đó chính là sứ mệnh của ta.</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Ví dụ, chắc cậu cũng từng thấy Etheric Sea ở Huanglong rồi nhỉ? Đó là một hiện tượng bầu trời độc đáo, gắn liền với sự xuất hiện của Tacet Field và Tacet Discord.</t>
+          <t>Ví dụ, chắc cậu cũng từng thấy Biển Ether ở Huanglong rồi nhỉ? Đó là một hiện tượng bầu trời độc đáo, gắn liền với sự xuất hiện của Tổ Tacet và Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Mỗi đêm, cả đám đông lại tụ tập ở Howling Tunnel để chơi Peaks of Prestige. Gió ở đó cứ như lời thì thầm của chính Exostrider... bầu không khí thật phi thực.</t>
+          <t>Mỗi đêm, cả đám đông lại tụ tập ở Đường Hầm Gào Thét để chơi Peaks of Prestige. Gió ở đó cứ như lời thì thầm của chính Exostrider... bầu không khí thật phi thực.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Tiếng rít trong Howling Tunnel... người Roya gọi đó là "Lối Đi của Exostrider". Nhiều nhà nghiên cứu, kể cả ông Duarte, đều báo cáo về ảo giác thính giác.</t>
+          <t>Tiếng rít trong Đường Hầm Gào Thét... người Roya gọi đó là "Lối Đi của Exostrider". Nhiều nhà nghiên cứu, kể cả ông Duarte, đều báo cáo về ảo giác thính giác.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên Cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
+          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên Cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
+          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên Cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
+          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên Cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
+          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên Cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
+          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên Cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
+          <t>Họ tạm gửi trang bị cho chúng tôi. Yên tâm đi, Viện Nghiên cứu có chuyên viên tư vấn thiết bị tại mỗi trạm để quản lý và giám sát đồ gửi.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Đừng có mà nói với tôi đó chỉ là ảo giác hay giấc mơ nhầm lẫn. Tôi biết rõ mình đã nghe gì. Howling Tunnel, hay "Lối Đi của Exostrider" như người Roya gọi, vẫn còn ẩn chứa những bí mật mà chúng ta chưa khám phá ra.</t>
+          <t>Đừng có mà nói với tôi đó chỉ là ảo giác hay giấc mơ nhầm lẫn. Tôi biết rõ mình đã nghe gì. Đường Hầm Gào Thét, hay "Lối Đi của Exostrider" như người Roya gọi, vẫn còn ẩn chứa những bí mật mà chúng ta chưa khám phá ra.</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Dự án của giáo sư nhất định cần trạm này làm điểm trung chuyển. Nếu không, toàn bộ thiết bị và vật tư này... Ta hiểu rồi, để sau bàn tiếp nhé.</t>
+          <t>Dự án của giáo sư nhất định cần trạm này làm điểm trung chuyển. Nếu không, toàn bộ thiết bị và vật tư này... Tao hiểu rồi, để sau bàn tiếp nhé.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Phép thuật, Gián điệp và Lời phàn nàn/i&gt;. Hội Chỉnh Huấn chắc chắn không muốn cuốn sách này được xuất bản. Kết quả là, nó đã bị gửi đến tận cùng thế giới, cùng với những người đó.</t>
+          <t>&lt;i&gt;Phép thuật, Gián điệp và Lời phàn nàn&lt;/i&gt;. Hội Huynh Đệ chắc chắn không muốn cuốn sách này được xuất bản. Vì vậy, nó bị lưu đày đến tận cùng thế giới, cùng với những con người đó.</t>
         </is>
       </c>
     </row>
@@ -22363,7 +22363,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Giai đoạn Ngủ Đông của Tacet Field thay đổi tùy theo thời gian hình thành. Thông thường, thời gian hình thành càng ngắn thì giai đoạn Ngủ Đông càng dài. Tuy nhiên, với giai đoạn Ngủ Đông dài hơn, các Tacet Discord sinh ra bên trong thường mạnh mẽ hơn.</t>
+          <t>Giai đoạn Ngủ Đông của Tổ Tacet thay đổi tùy theo thời gian hình thành. Thông thường, thời gian hình thành càng ngắn thì giai đoạn Ngủ Đông càng dài. Tuy nhiên, với giai đoạn Ngủ Đông dài hơn, các Tacet Discord sinh ra bên trong thường mạnh mẽ hơn.</t>
         </is>
       </c>
     </row>
@@ -22428,7 +22428,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Giai đoạn Ngủ Đông của Tacet Field thay đổi tùy theo thời gian hình thành. Thông thường, thời gian hình thành càng ngắn thì giai đoạn Ngủ Đông càng dài. Tuy nhiên, với giai đoạn Ngủ Đông dài hơn, các Tacet Discord sinh ra trong Tacet Field đó thường mạnh mẽ hơn.</t>
+          <t>Giai đoạn Ngủ Đông của Tổ Tacet thay đổi tùy theo thời gian hình thành. Thông thường, thời gian hình thành càng ngắn thì giai đoạn Ngủ Đông càng dài. Tuy nhiên, với giai đoạn Ngủ Đông dài hơn, các Tacet Discord sinh ra trong Tổ Tacet đó thường mạnh mẽ hơn.</t>
         </is>
       </c>
     </row>
@@ -22493,7 +22493,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Rời khỏi Gorges of Spirits, cậu bắt gặp một Tacet Field mới hình thành. Ở trung tâm có một người phụ nữ tên Baizhi, dường như đang điều tra điều gì đó. Cậu quyết định lướt xuống gặp cô ấy.</t>
+          <t>Rời khỏi Gorges of Spirits, cậu bắt gặp một Tổ Tacet mới hình thành. Ở trung tâm có một người phụ nữ tên Baizhi, dường như đang điều tra điều gì đó. Cậu quyết định lướt xuống gặp cô ấy.</t>
         </is>
       </c>
     </row>
@@ -22558,7 +22558,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Chỉ có thể hấp thụ khi cấp độ Data Bank của cậu bằng hoặc cao hơn cấp độ của Discord. Khi đó, Terminal sẽ chuyển hóa Dư Âm của nó thành "Echo" để sử dụng trong chiến đấu.</t>
+          <t>Chỉ có thể hấp thụ khi cấp độ Kho Dữ Liệu của cậu bằng hoặc cao hơn cấp độ của Tacet Discord. Khi đó, Thiết bị đầu cuối sẽ chuyển hóa Dư Âm của nó thành "Echo" để sử dụng trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Discord mà cậu vừa đánh bại để lại một bóng vàng mờ ảo. Chixia giải thích đó là tàn tích còn sót lại sau khi một Discord bị tiêu diệt, và có thể được hấp thụ bởi Pangu Terminal dưới dạng Echo để hỗ trợ chiến đấu. Cậu thử hấp thụ nó bằng Terminal của mình, nhưng không thành công.</t>
+          <t>Tacet Discord mà cậu vừa đánh bại để lại một bóng vàng mờ ảo. Chixia giải thích đó là tàn tích còn sót lại sau khi một Tacet Discord bị tiêu diệt, và có thể được hấp thụ bởi Thiết bị đầu cuối Pangu dưới dạng Echo để hỗ trợ chiến đấu. Cậu thử hấp thụ nó bằng Thiết bị đầu cuối của mình, nhưng không thành công.</t>
         </is>
       </c>
     </row>
@@ -22753,7 +22753,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Ngày xưa có một người cực kỳ mạnh mẽ. Như thể họ nắm giữ cả vũ trụ trong lòng bàn tay. Vì thời đó chưa có Terminal, họ hấp thụ các Tacet Discord bằng chính đôi tay trần!</t>
+          <t>Ngày xưa có một người cực kỳ mạnh mẽ. Như thể họ nắm giữ cả vũ trụ trong lòng bàn tay. Vì thời đó chưa có Thiết bị đầu cuối, họ hấp thụ các Tacet Discord bằng chính đôi tay trần!</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22818,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Nào, chuyện đó đã lâu lắm rồi. Resonators chúng ta sống lâu hơn chút, nhưng cũng chỉ khoảng trăm năm thôi. Còn lịch sử của Huanglong thì đã kéo dài ít nhất cả ngàn năm...</t>
+          <t>Nào, chuyện đó đã lâu lắm rồi. Resonator chúng ta sống lâu hơn chút, nhưng cũng chỉ khoảng trăm năm thôi. Còn lịch sử của Huanglong thì đã kéo dài ít nhất cả ngàn năm...</t>
         </is>
       </c>
     </row>
@@ -22883,7 +22883,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Khả năng hấp thụ Echo bằng chính cơ thể của cậu khiến Chixia phải kinh ngạc. Những ghi chép cổ xưa, có từ trước khi Huanglong thành lập và trước khi Terminal ra đời, kể về một sinh thể bí ẩn ngoài vũ trụ có thể hấp thụ tàn tích của Tacet Discord. Truyền thuyết kể rằng chúng đã góp phần mở ra trang sử đầu tiên của Huanglong.</t>
+          <t>Khả năng hấp thụ Echo bằng chính cơ thể của cậu khiến Chixia phải kinh ngạc. Những ghi chép cổ xưa, có từ trước khi Huanglong thành lập và trước khi Thiết bị đầu cuối ra đời, kể về một sinh thể bí ẩn ngoài vũ trụ có thể hấp thụ tàn tích của Tacet Discord. Truyền thuyết kể rằng chúng đã góp phần mở ra trang sử đầu tiên của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Tấn Châu luôn là tuyến phòng thủ trọng yếu chống lại các đợt bùng phát Discord, bảo vệ Huanglong. Chúng ta gánh trên vai trách nhiệm nặng nề, không được phép lùi bước hay thất bại.</t>
+          <t>Tấn Châu luôn là tuyến phòng thủ trọng yếu chống lại các đợt bùng phát Tacet Discord, bảo vệ Huanglong. Chúng ta gánh trên vai trách nhiệm nặng nề, không được phép lùi bước hay thất bại.</t>
         </is>
       </c>
     </row>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Khi Tacet Field gây nhiễu đã bị khuất phục, một thông báo holographic truyền đi khắp Jinzhou. Jinhsi, vị Quan Chấp, đang đợi một vị khách quý tại Tòa Thị Chính và gửi lời mời đến để trò chuyện.</t>
+          <t>Khi Tổ Tacet gây nhiễu đã bị khuất phục, một thông báo holographic truyền đi khắp Jinzhou. Jinhsi, vị Quan Chấp, đang đợi một vị khách quý tại Tòa Thị Chính và gửi lời mời đến để trò chuyện.</t>
         </is>
       </c>
     </row>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Chúng ta đã giao phó sinh mạng cho nhau rồi mà. Ta chưa bao giờ thấy nhiều TD dồn lại thế này, mà con Elite kia kinh thật! Nhưng mà cậu cũng đã giải quyết gần hết rồi, hihi.</t>
+          <t>Chúng ta đã giao phó sinh mạng cho nhau rồi mà. Tao chưa bao giờ thấy nhiều TD dồn lại thế này, mà con Elite kia kinh thật! Nhưng mà cậu cũng đã giải quyết gần hết rồi, hihi.</t>
         </is>
       </c>
     </row>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Với việc thiếu dữ liệu về cậu và những dấu hiệu thể chất bất thường này, tôi đề nghị cậu hấp thụ thêm một Reverberation khác qua Terminal khi tìm thấy. Nhưng nhớ là phải tiến hành cẩn thận đấy.</t>
+          <t>Với việc thiếu dữ liệu về cậu và những dấu hiệu thể chất bất thường này, tôi đề nghị cậu hấp thụ thêm một Reverberation khác qua Thiết bị đầu cuối khi tìm thấy. Nhưng nhớ là phải tiến hành cẩn thận đấy.</t>
         </is>
       </c>
     </row>
@@ -23403,7 +23403,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Chết rồi, đúng như tớ đoán. &lt;ano=Terminals&gt;Bình chứa&lt;/ano&gt; của chúng ta bị hỏng vì ảnh hưởng của &lt;color=Highlight&gt;Etheric Seaic&lt;/color&gt;. Giờ không gửi hay nhận tin cầu cứu được nữa. Mau đến chỗ hẹn với Baizhi và rời khỏi đây thôi.</t>
+          <t>Chết rồi, đúng như tớ đoán. &lt;ano=Terminals&gt;Bình chứa&lt;/ano&gt; của chúng ta bị hỏng vì ảnh hưởng của &lt;color=Highlight&gt;Biển Etheric&lt;/color&gt;. Giờ không gửi hay nhận tin cầu cứu được nữa. Mau đến chỗ hẹn với Baizhi và rời khỏi đây thôi.</t>
         </is>
       </c>
     </row>
@@ -23533,7 +23533,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Thức tỉnh bên cạnh Chixia và Yangyang, cậu nhận ra mọi ký ức của mình đã bị xóa sạch. Cậu là một Rover ở vùng đất xa lạ này, và đây là cái tên họ đặt cho cậu. Khi đang cố gắng lấy lại bình tĩnh, Yangyang mời cậu cùng tham gia, đúng lúc một Tacet Field đáng sợ bắt đầu trải rộng sự hiện diện u ám của nó.</t>
+          <t>Thức tỉnh bên cạnh Chixia và Yangyang, cậu nhận ra mọi ký ức của mình đã bị xóa sạch. Cậu là một Vận Mệnh Giả ở vùng đất xa lạ này, và đây là cái tên họ đặt cho cậu. Khi đang cố gắng lấy lại bình tĩnh, Yangyang mời cậu cùng tham gia, đúng lúc một Tổ Tacet đáng sợ bắt đầu trải rộng sự hiện diện u ám của nó.</t>
         </is>
       </c>
     </row>
@@ -23598,7 +23598,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tay cậu có Tacet Mark, lại còn mang theo &lt;ano=Terminal&gt;bình hồ lô&lt;/ano&gt;. Đó là bằng chứng cho thấy cậu là Resonator. Tuy nhiên, bình hồ lô của cậu trông hơi khác với loại chúng tôi dùng.</t>
+          <t>Tay cậu có Dấu Tacet, lại còn mang theo &lt;ano=Terminal&gt;bình hồ lô&lt;/ano&gt;. Đó là bằng chứng cho thấy cậu là Resonator. Tuy nhiên, bình hồ lô của cậu trông hơi khác với loại chúng tôi dùng.</t>
         </is>
       </c>
     </row>
@@ -23663,7 +23663,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Tay cậu có Tacet Mark, lại còn mang theo &lt;ano=Terminal&gt;bình hồ lô&lt;/ano&gt;. Đó là bằng chứng cho thấy cậu là Resonator. Tuy nhiên, bình hồ lô của cậu trông hơi khác với loại chúng tôi dùng.</t>
+          <t>Tay cậu có Dấu Tacet, lại còn mang theo &lt;ano=Terminal&gt;bình hồ lô&lt;/ano&gt;. Đó là bằng chứng cho thấy cậu là Resonator. Tuy nhiên, bình hồ lô của cậu trông hơi khác với loại chúng tôi dùng.</t>
         </is>
       </c>
     </row>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Khi nhìn bức tượng, một ảo ảnh về Sentinel thoáng qua trong tâm trí cậu. Ngay khi định hỏi Yangyang giải thích, một tiếng kêu thất thanh vang lên. Chixia đang bị tấn công bởi một Discord cấp Elite!</t>
+          <t>Khi nhìn bức tượng, một ảo ảnh về Sentinel thoáng qua trong tâm trí cậu. Ngay khi định hỏi Yangyang giải thích, một tiếng kêu thất thanh vang lên. Chixia đang bị tấn công bởi một Tacet Discord cấp Elite!</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Yes. Chúng ta cần tiến hành kiểm tra thể chất để xác định xem có bệnh lý nào không. Nếu không phát hiện vấn đề y tế, chúng ta sẽ tiếp tục theo dõi và phân tích để hiểu chuyện gì đã xảy ra với cơ thể cậu.</t>
+          <t>Đúng vậy. Chúng ta cần tiến hành kiểm tra thể chất để xác định xem có bệnh lý nào không. Nếu không phát hiện vấn đề y tế, chúng ta sẽ tiếp tục theo dõi và phân tích để hiểu chuyện gì đã xảy ra với cơ thể cậu.</t>
         </is>
       </c>
     </row>
@@ -24248,7 +24248,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Jinzhou có biết bao nhiêu là trò vui! Chúng ta có thể đi xem múa lân, kịch anh hùng, hài độc thoại, rồi còn giải đấu võ thuật nữa... Chưa kể đủ loại món ngon để thử. Ngươi nghĩ gì, ta có hết.</t>
+          <t>Jinzhou có biết bao nhiêu là trò vui! Chúng ta có thể đi xem múa lân, kịch anh hùng, hài độc thoại, rồi còn giải đấu võ thuật nữa... Chưa kể đủ loại món ngon để thử. Mày nghĩ gì, tao có hết.</t>
         </is>
       </c>
     </row>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Lữ Đoàn Kỵ Sĩ Đêm dưới quyền Đại Tướng Jiyan là lực lượng đồn trú tại Jinzhou. Họ bao gồm Tiên Phong – đảm nhiệm tấn công các Tacet Discord, và Rearguards – phụ trách phòng thủ thành phố.</t>
+          <t>Lữ Đoàn Kỵ Sĩ Đêm dưới quyền Đại Tướng Jiyan là lực lượng đồn trú tại Jinzhou. Họ bao gồm Tiên Phong – đảm nhiệm tấn công các Tacet Discord, và Hậu Vệ – phụ trách phòng thủ thành phố.</t>
         </is>
       </c>
     </row>
@@ -24638,7 +24638,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Ý tôi là, đây là Huanglong! Mà lại là Jinzhou nữa chứ. Nơi này chưa bao giờ thực sự an toàn trong hàng nghìn năm qua. Dù bao đợt bùng phát Echo, chúng ta vẫn vượt qua được.</t>
+          <t>Ý tôi là, đây là Huanglong! Mà lại là Jinzhou nữa chứ. Nơi này chưa bao giờ thực sự an toàn trong hàng nghìn năm qua. Dù bao đợt bùng phát Tổ Tacet, chúng ta vẫn vượt qua được.</t>
         </is>
       </c>
     </row>
@@ -24768,7 +24768,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Nhưng Rover đã mất hết ký ức, chắc chắn sẽ quên mất bất kỳ phương pháp giải mã nào mà hai người đã thống nhất. Điều này thật chẳng hợp lý. Or maybe... cô ấy đang cố khiến Rover chú ý đến điều gì khác?</t>
+          <t>Nhưng Vận Mệnh Giả đã mất hết ký ức, chắc chắn sẽ quên mất bất kỳ phương pháp giải mã nào mà hai người đã thống nhất. Điều này thật chẳng hợp lý. Hay là... cô ấy đang cố khiến Vận Mệnh Giả chú ý đến điều gì khác?</t>
         </is>
       </c>
     </row>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Sundial ở Huanglong thường có các vạch chia cho mười hai &lt;ano=Time Periods&gt;Thời Thần&lt;/ano&gt; trong ngày, mỗi Thời Thần dài hai tiếng, một số còn thể hiện mùa hoặc tháng. Tuy nhiên, thiết kế của chiếc đồng hồ này có vẻ hơi khác lạ...</t>
+          <t>Đồng hồ Mặt Trời ở Huanglong thường có các vạch chia cho mười hai &lt;ano=Time Periods&gt;Thời Thần&lt;/ano&gt; trong ngày, mỗi Thời Thần dài hai tiếng, một số còn thể hiện mùa hoặc tháng. Tuy nhiên, thiết kế của chiếc đồng hồ này có vẻ hơi khác lạ...</t>
         </is>
       </c>
     </row>
@@ -24963,7 +24963,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Thông thường, Thanh Long đại diện cho &lt;color=Highlight&gt;phương Đông&lt;/color&gt;, White Tiger tượng trưng cho &lt;color=Highlight&gt;phương Tây&lt;/color&gt;, Chu Tước tượng trưng cho &lt;color=Highlight&gt;phương Nam&lt;/color&gt;, và cuối cùng là Black Tortoise cho &lt;color=Highlight&gt;phương Bắc&lt;/color&gt;.</t>
+          <t>Thông thường, Thanh Long đại diện cho &lt;color=Highlight&gt;phương Đông&lt;/color&gt;, Bạch Hổ tượng trưng cho &lt;color=Highlight&gt;phương Tây&lt;/color&gt;, Chu Tước tượng trưng cho &lt;color=Highlight&gt;phương Nam&lt;/color&gt;, và cuối cùng là Huyền Vũ cho &lt;color=Highlight&gt;phương Bắc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25093,7 +25093,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Nhưng không phải lúc nào chúng cũng có sẵn để mua đâu. Những đợt bùng phát Discord thường xuyên làm gián đoạn vận chuyển và gây ra tình trạng khan hiếm. Dù Midnight Rangers đã cải thiện tình hình trong những năm gần đây, nhưng vẫn thế thôi.</t>
+          <t>Nhưng không phải lúc nào chúng cũng có sẵn để mua đâu. Những đợt bùng phát Tacet Discord thường xuyên làm gián đoạn vận chuyển và gây ra tình trạng khan hiếm. Dù Midnight Rangers đã cải thiện tình hình trong những năm gần đây, nhưng vẫn thế thôi.</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Xin thứ lỗi vì tôi không thể đưa ra câu trả lời tốt hơn. Quận trưởng có nhiệm vụ phải tự mình xử lý, nhưng bà ấy chưa bao giờ quên cuộc hẹn với cậu dù chỉ trong giây lát.</t>
+          <t>Xin thứ lỗi vì tôi không thể đưa ra câu trả lời tốt hơn. Quận trưởng có nhiệm vụ phải tự mình xử lý, nhưng bà ấy chưa bao giờ quên cuộc hẹn với bạn dù chỉ trong giây lát.</t>
         </is>
       </c>
     </row>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Mô-đun Công cụ trên Terminal của cậu đã được nâng cấp lên phiên bản mới nhất. Giờ đây, tất cả các Công cụ như Sensor, Bay Lơ Lửng và Móc Kéo đều hoạt động bình thường.</t>
+          <t>Mô-đun Tiện Ích trên Thiết bị đầu cuối của cậu đã được nâng cấp lên phiên bản mới nhất. Giờ đây, tất cả các Tiện Ích như Cảm Biến, Bay Lơ Lửng và Móc Kéo đều hoạt động bình thường.</t>
         </is>
       </c>
     </row>
@@ -27433,7 +27433,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Quả lựu đạn đó là một trong số chúng. Với sự phát triển nhanh chóng của Weapons Echo, những loại chất nổ thô sơ này dần bị thay thế bởi vũ khí tiên tiến hơn.</t>
+          <t>Quả lựu đạn đó là một trong số chúng. Với sự phát triển nhanh chóng của Vũ khí Echo, những loại chất nổ thô sơ này dần bị thay thế bởi vũ khí tiên tiến hơn.</t>
         </is>
       </c>
     </row>
@@ -32763,7 +32763,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Cơ khí Tự động không phải chuyên môn của ta. Ta chuyên phát triển Weapons Tacetite, nhưng lý thuyết nền tảng của các công nghệ ứng dụng này khá tương đồng.</t>
+          <t>Cơ khí Tự động không phải chuyên môn của ta. Ta chuyên phát triển Vũ khí Tacetite, nhưng lý thuyết nền tảng của các công nghệ ứng dụng này khá tương đồng.</t>
         </is>
       </c>
     </row>
